--- a/approaches/CoLA/docs/training_runs_plan.xlsx
+++ b/approaches/CoLA/docs/training_runs_plan.xlsx
@@ -12,8 +12,8 @@
     <sheet name="tier_summary" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">matrix!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">runs!$A$1:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">matrix!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">runs!$A$1:$H$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">tier_summary!$A$1:$B$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="40">
   <si>
     <t>tier</t>
   </si>
@@ -47,6 +47,15 @@
     <t>notes</t>
   </si>
   <si>
+    <t>tier12</t>
+  </si>
+  <si>
+    <t>tier12_base</t>
+  </si>
+  <si>
+    <t>tier72</t>
+  </si>
+  <si>
     <t>LoRA</t>
   </si>
   <si>
@@ -59,16 +68,16 @@
     <t>baseline</t>
   </si>
   <si>
-    <t>flat</t>
-  </si>
-  <si>
-    <t>experts-all</t>
-  </si>
-  <si>
-    <t>experts-expertonly</t>
-  </si>
-  <si>
-    <t>experts-best</t>
+    <t>hydra-flat</t>
+  </si>
+  <si>
+    <t>hydra-exp-lpr</t>
+  </si>
+  <si>
+    <t>colaflat</t>
+  </si>
+  <si>
+    <t>colaexp-lpr</t>
   </si>
   <si>
     <t>stage1</t>
@@ -80,82 +89,52 @@
     <t>all</t>
   </si>
   <si>
-    <t>expert_only</t>
-  </si>
-  <si>
     <t>learned</t>
   </si>
   <si>
-    <t>bias</t>
-  </si>
-  <si>
     <t>Rank-8 LoRA baseline (finetuning_type=lora)</t>
   </si>
   <si>
-    <t>Shared-A multi-B, lora_num=3</t>
-  </si>
-  <si>
-    <t>use_hydralora_experts=True, JSON experts, LPR on</t>
-  </si>
-  <si>
-    <t>Expert guidance only, free B heads</t>
-  </si>
-  <si>
-    <t>Classic collaborative A/B (num_A=1,num_B=3)</t>
-  </si>
-  <si>
-    <t>Family-level experts, LPR on from start</t>
-  </si>
-  <si>
-    <t>Hard expert guidance, free B usage</t>
-  </si>
-  <si>
-    <t>Carry best hyperparams from tier-12</t>
-  </si>
-  <si>
-    <t>Same lora_num as tier-12 winner</t>
-  </si>
-  <si>
-    <t>Full guidance; promoted config</t>
-  </si>
-  <si>
-    <t>Expert-guided ablation</t>
-  </si>
-  <si>
-    <t>Mirror tier-12 winner</t>
-  </si>
-  <si>
-    <t>Reference run for largest tier</t>
-  </si>
-  <si>
-    <t>Best Hydra config from tier-72</t>
-  </si>
-  <si>
-    <t>Best CoLA config from tier-72</t>
-  </si>
-  <si>
-    <t>CoLA|experts-all</t>
-  </si>
-  <si>
-    <t>CoLA|experts-best</t>
-  </si>
-  <si>
-    <t>CoLA|experts-expertonly</t>
-  </si>
-  <si>
-    <t>CoLA|flat</t>
-  </si>
-  <si>
-    <t>HydraLoRA|experts-all</t>
-  </si>
-  <si>
-    <t>HydraLoRA|experts-best</t>
-  </si>
-  <si>
-    <t>HydraLoRA|experts-expertonly</t>
-  </si>
-  <si>
-    <t>HydraLoRA|flat</t>
+    <t>LoRA baseline on original tokenizer/model (no extension)</t>
+  </si>
+  <si>
+    <t>Shared-A multi-B baseline (lora_num=3, no experts)</t>
+  </si>
+  <si>
+    <t>use_hydralora_experts=True with JSON clusters, Stage 1 LPR</t>
+  </si>
+  <si>
+    <t>Classic CoLA (num_A=1,num_B=3, no experts)</t>
+  </si>
+  <si>
+    <t>CoLA experts with shared A per cluster, Stage 1 LPR</t>
+  </si>
+  <si>
+    <t>Same hyperparams as tier12 LoRA baseline</t>
+  </si>
+  <si>
+    <t>Mirror tier12 Hydra flat baseline</t>
+  </si>
+  <si>
+    <t>Tier72 clusters + Hydra experts with Stage 1 LPR</t>
+  </si>
+  <si>
+    <t>Same collaborative settings as tier12 CoLA flat</t>
+  </si>
+  <si>
+    <t>Tier72 CoLA experts with Stage 1 LPR guidance</t>
+  </si>
+  <si>
+    <t>CoLA|colaexp-lpr</t>
+  </si>
+  <si>
+    <t>CoLA|colaflat</t>
+  </si>
+  <si>
+    <t>HydraLoRA|hydra-exp-lpr</t>
+  </si>
+  <si>
+    <t>HydraLoRA|hydra-flat</t>
   </si>
   <si>
     <t>LoRA|baseline</t>
@@ -533,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -563,499 +542,331 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
         <v>20</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C7" t="s">
         <v>18</v>
       </c>
-      <c r="F4" t="s">
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
-      </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="2">
         <v>0.1</v>
       </c>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8">
-        <v>12</v>
+      <c r="A8" t="s">
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
         <v>16</v>
       </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9">
-        <v>72</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10">
-        <v>72</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11">
-        <v>72</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="D11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="C12" t="s">
         <v>18</v>
       </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12">
-        <v>72</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.1</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13">
-        <v>72</v>
-      </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14">
-        <v>72</v>
-      </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15">
-        <v>72</v>
-      </c>
-      <c r="B15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16">
-        <v>200</v>
-      </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17">
-        <v>200</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18">
-        <v>200</v>
-      </c>
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18" t="s">
-        <v>36</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H18"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1">
-        <v>12</v>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1066,86 +877,50 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1">
-        <v>72</v>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1">
-        <v>200</v>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
-  <conditionalFormatting sqref="B2:J5">
+  <autoFilter ref="A1:F4"/>
+  <conditionalFormatting sqref="B2:F5">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1171,31 +946,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1">
-        <v>12</v>
+      <c r="A2" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="1">
-        <v>72</v>
+      <c r="A3" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="1">
-        <v>200</v>
+      <c r="A4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
